--- a/accountant-skill/data/output/Aug2025/trial_balance_Aug2025.xlsx
+++ b/accountant-skill/data/output/Aug2025/trial_balance_Aug2025.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dr: 1,619,886,399.70 | Cr: 1,621,100,098.63</t>
+          <t>Dr: 2,092,190,455.66 | Cr: 2,093,404,154.59</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr: 1,696,964,076.98 | Cr: 1,698,177,775.91</t>
+          <t>Dr: 2,168,513,258.69 | Cr: 2,169,726,957.62</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>814782.2800000003</v>
+        <v>4790394.720000004</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>7190701.07</v>
@@ -658,7 +658,7 @@
         <v>4790395.09</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1585523.7</v>
+        <v>7190700.700000005</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>447284.7600000016</v>
+        <v>7452015.239999998</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>12692758.27</v>
@@ -680,7 +680,7 @@
         <v>7452014.79</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4793458.719999998</v>
+        <v>12692758.72</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3005485.010000005</v>
+        <v>37467131.01000001</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>32444705.19</v>
@@ -702,7 +702,7 @@
         <v>37467131.49</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2016941.289999999</v>
+        <v>32444704.71</v>
       </c>
     </row>
     <row r="11">
@@ -775,12 +775,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
     </row>
     <row r="16">
@@ -792,13 +792,15 @@
           <t>Buildings &amp; Structures</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="n">
+        <v>133000000</v>
+      </c>
       <c r="D16" s="4" t="n">
         <v>316445000</v>
       </c>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n">
-        <v>316445000</v>
+        <v>449445000</v>
       </c>
     </row>
     <row r="17">
@@ -811,14 +813,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3325000.68</v>
+        <v>23275000.68000001</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n">
         <v>554167</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3879167.68</v>
+        <v>23829167.68000001</v>
       </c>
     </row>
     <row r="18">
@@ -831,12 +833,12 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>69520000</v>
+        <v>135920000</v>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>69520000</v>
+        <v>135920000</v>
       </c>
     </row>
     <row r="19">
@@ -849,14 +851,14 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7655213.33</v>
+        <v>20030513.33</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n">
         <v>1596316</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9251529.33</v>
+        <v>21626829.33</v>
       </c>
     </row>
     <row r="20">
@@ -897,12 +899,12 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>98881000</v>
+        <v>106081000</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>98881000</v>
+        <v>106081000</v>
       </c>
     </row>
     <row r="23">
@@ -915,14 +917,14 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1698480.33</v>
+        <v>3408480.33</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n">
         <v>354917</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2053397.33</v>
+        <v>3763397.33</v>
       </c>
     </row>
     <row r="24">
@@ -1069,12 +1071,12 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1000000000</v>
+        <v>1439530823</v>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n">
-        <v>1000000000</v>
+        <v>1439530823</v>
       </c>
     </row>
     <row r="34">
@@ -1625,7 +1627,7 @@
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>1621100098.63</v>
+        <v>2093404154.59</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>727098924.4</v>
@@ -1634,7 +1636,7 @@
         <v>727098924.4000001</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>1698177775.91</v>
+        <v>2169726957.62</v>
       </c>
     </row>
   </sheetData>
